--- a/demo/demo4-complete/output/selected-ultimates.xlsx
+++ b/demo/demo4-complete/output/selected-ultimates.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paid Loss" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reported Count" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closed Count" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exposure" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -599,22 +600,22 @@
         <v>45008437.7</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>45008437.7</v>
+        <v>45571043.17125</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>63882090.39307072</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>45008437.7</v>
+        <v>45797105.4826305</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>45008437.7</v>
+        <v>46543111</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0</v>
+        <v>1534673.299999997</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.0300000011920929</v>
+        <v>1534673.329999998</v>
       </c>
     </row>
     <row r="4">
@@ -630,22 +631,22 @@
         <v>59922623.84</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>61133060.841568</v>
+        <v>61897224.1020876</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>63453604.66974273</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>61179007.70034974</v>
+        <v>61946874.62392249</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>61133060.841568</v>
+        <v>61987456</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1210437.001567997</v>
+        <v>2064832.159999996</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1865362.501567997</v>
+        <v>2719757.659999996</v>
       </c>
     </row>
     <row r="5">
@@ -661,22 +662,22 @@
         <v>35372411.74</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>37281411.98767959</v>
+        <v>37751083.43963938</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>59549252.9255448</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>38421640.09598522</v>
+        <v>39124572.20170287</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>37281411.98767959</v>
+        <v>39184364</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1909000.247679591</v>
+        <v>3811952.259999998</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>2373669.767679594</v>
+        <v>4276621.780000001</v>
       </c>
     </row>
     <row r="6">
@@ -692,22 +693,22 @@
         <v>55323529.15</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>60804900.15690639</v>
+        <v>61547303.11634473</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>54342744.02862492</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>60222357.05343512</v>
+        <v>60818765.14605574</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>60804900.15690639</v>
+        <v>61004941</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>5481371.00690639</v>
+        <v>5681411.850000001</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>8382540.61690639</v>
+        <v>8582581.460000001</v>
       </c>
     </row>
     <row r="7">
@@ -723,22 +724,22 @@
         <v>40379699.29</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>46985591.30256086</v>
+        <v>47559266.15350163</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>52619444.17055962</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>47777677.18738035</v>
+        <v>48323152.7596875</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>46985591.30256086</v>
+        <v>48041441</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>6605892.012560859</v>
+        <v>7661741.710000001</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>9060943.782560855</v>
+        <v>10116793.48</v>
       </c>
     </row>
     <row r="8">
@@ -754,22 +755,22 @@
         <v>34927144.1</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>43644400.72906783</v>
+        <v>44152598.66635146</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>48440622.50779771</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>44602367.73965085</v>
+        <v>45048558.82098766</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>43644400.72906783</v>
+        <v>44635788</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>8717256.629067831</v>
+        <v>9708643.899999999</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>12883901.06906783</v>
+        <v>13875288.34</v>
       </c>
     </row>
     <row r="9">
@@ -785,22 +786,22 @@
         <v>55221806.45</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>76649961.17653154</v>
+        <v>77682093.32922915</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>46245248.98674966</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>68150062.84366995</v>
+        <v>68592732.93419862</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>74524986.59331614</v>
+        <v>72020039</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>19303180.14331613</v>
+        <v>16798232.55</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>28337972.05331614</v>
+        <v>25833024.46</v>
       </c>
     </row>
     <row r="10">
@@ -816,22 +817,22 @@
         <v>27042042.17</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>44989906.31774423</v>
+        <v>45637564.02906246</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>52424249.22500541</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>47955695.47909316</v>
+        <v>48402872.73027548</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>46472800.89841869</v>
+        <v>47221287</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>19430758.72841869</v>
+        <v>20179244.83</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>23369844.04841869</v>
+        <v>24118330.15</v>
       </c>
     </row>
     <row r="11">
@@ -847,22 +848,22 @@
         <v>21336027.8</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>47466317.46963407</v>
+        <v>48099213.74700803</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>47439177.78386472</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>47451377.02578881</v>
+        <v>47731958.98674875</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>47455112.13675013</v>
+        <v>47756784</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>26119084.33675013</v>
+        <v>26420756.2</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>29535518.41675013</v>
+        <v>29837190.28</v>
       </c>
     </row>
     <row r="12">
@@ -878,22 +879,22 @@
         <v>15929923.89</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>64141668.35204265</v>
+        <v>64878397.67714732</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>36626176.32642927</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>43459794.86217109</v>
+        <v>43563088.33341151</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>43459794.86217109</v>
+        <v>47479305</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>27529870.97217109</v>
+        <v>31549381.11</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>30198438.59217109</v>
+        <v>34217948.73</v>
       </c>
     </row>
   </sheetData>
@@ -999,22 +1000,22 @@
         <v>45008437.67</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>45008437.67</v>
+        <v>45863597.98573</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>63882090.39307072</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>45008437.67</v>
+        <v>46199565.95014557</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>45008437.67</v>
+        <v>46848515</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0</v>
+        <v>1840077.329999998</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0</v>
+        <v>1840077.329999998</v>
       </c>
     </row>
     <row r="4">
@@ -1030,22 +1031,22 @@
         <v>59267698.34</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>61839916.44795601</v>
+        <v>63014874.86046717</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>63453604.66974273</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>61907037.46465674</v>
+        <v>63040963.9075975</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>61839916.44795601</v>
+        <v>63169814</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>2572218.107956007</v>
+        <v>3902115.659999996</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>2572218.107956007</v>
+        <v>3902115.659999996</v>
       </c>
     </row>
     <row r="5">
@@ -1061,22 +1062,22 @@
         <v>34907742.22</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>38557110.6927636</v>
+        <v>39271138.41079672</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>59549252.9255448</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>40543983.17007448</v>
+        <v>41524229.38831383</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>38557110.6927636</v>
+        <v>40848317</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3649368.472763598</v>
+        <v>5940574.780000001</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3649368.472763598</v>
+        <v>5940574.780000001</v>
       </c>
     </row>
     <row r="6">
@@ -1092,22 +1093,22 @@
         <v>52422359.54</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>61371138.34975644</v>
+        <v>62525344.80593821</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>54342744.02862492</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>60346299.18498309</v>
+        <v>61203181.84391326</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>61371138.34975644</v>
+        <v>61785674</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>8948778.809756443</v>
+        <v>9363314.460000001</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>8948778.809756443</v>
+        <v>9363314.460000001</v>
       </c>
     </row>
     <row r="7">
@@ -1123,22 +1124,22 @@
         <v>37924647.52</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>48207987.81583902</v>
+        <v>49114635.01634339</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>52619444.17055962</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>49149004.21065583</v>
+        <v>49913149.97221549</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>48207987.81583902</v>
+        <v>49529430</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>10283340.29583902</v>
+        <v>11604782.48</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>10283340.29583902</v>
+        <v>11604782.48</v>
       </c>
     </row>
     <row r="8">
@@ -1154,22 +1155,22 @@
         <v>30760499.66</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>43367215.93912094</v>
+        <v>44166888.1278176</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>48440622.50779771</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>44842039.62320808</v>
+        <v>45464134.6791361</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>43367215.93912094</v>
+        <v>44769749</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>12606716.27912094</v>
+        <v>14009249.34</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>12606716.27912094</v>
+        <v>14009249.34</v>
       </c>
     </row>
     <row r="9">
@@ -1185,22 +1186,22 @@
         <v>46187014.54</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>74818341.42213292</v>
+        <v>76052061.5130576</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>46245248.98674966</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>63884049.99036845</v>
+        <v>64347160.44259194</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>72084768.5641918</v>
+        <v>69294515</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>25897754.0241918</v>
+        <v>23107500.46</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>25897754.0241918</v>
+        <v>23107500.46</v>
       </c>
     </row>
     <row r="10">
@@ -1216,22 +1217,22 @@
         <v>23102956.85</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>45365952.33464483</v>
+        <v>46079778.62356748</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>52424249.22500541</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>48829757.75947612</v>
+        <v>49243330.50274949</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>47097855.04706047</v>
+        <v>47820600</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>23994898.19706047</v>
+        <v>24717643.15</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>23994898.19706047</v>
+        <v>24717643.15</v>
       </c>
     </row>
     <row r="11">
@@ -1247,22 +1248,22 @@
         <v>17919593.72</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>48513253.33383591</v>
+        <v>48751204.04683225</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>47439177.78386472</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>47835914.67857727</v>
+        <v>47921442.33593122</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>48005249.34239192</v>
+        <v>48229234</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>30085655.62239192</v>
+        <v>30309640.28</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>30085655.62239192</v>
+        <v>30309640.28</v>
       </c>
     </row>
     <row r="12">
@@ -1278,22 +1279,22 @@
         <v>13261356.27</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>64839242.04258323</v>
+        <v>65485581.26640987</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>36626176.32642927</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>42396501.58231553</v>
+        <v>42470437.66225389</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>42396501.58231553</v>
+        <v>46781253</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>29135145.31231553</v>
+        <v>33519896.73</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>29135145.31231553</v>
+        <v>33519896.73</v>
       </c>
     </row>
   </sheetData>
@@ -1408,13 +1409,13 @@
         <v>4930</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>4930</v>
+        <v>5011</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -1439,13 +1440,13 @@
         <v>4943</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>4943</v>
+        <v>5012</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
@@ -1470,13 +1471,13 @@
         <v>4919.891364408806</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4911.6672</v>
+        <v>4956</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>47.66719999999987</v>
+        <v>92</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>207.6671999999999</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
@@ -1492,22 +1493,22 @@
         <v>4886</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>4987.16873424</v>
+        <v>4985.688569399999</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>5102.48838127437</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>4989.508086153917</v>
+        <v>4988.02397523008</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>4987.16873424</v>
+        <v>4992</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>101.16873424</v>
+        <v>106</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>315.16873424</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7">
@@ -1523,22 +1524,22 @@
         <v>4767</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4970.803961648448</v>
+        <v>4971.2743580346</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4796.776590799303</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4963.668804461006</v>
+        <v>4964.10407999053</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>4970.803961648448</v>
+        <v>4960</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>203.8039616484475</v>
+        <v>193</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>615.8039616484475</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -1554,22 +1555,22 @@
         <v>4597</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4998.219921514037</v>
+        <v>4997.734114411615</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>4287.219569156572</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>4941.146101224253</v>
+        <v>4940.762812907539</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>4998.219921514037</v>
+        <v>4945</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>401.2199215140372</v>
+        <v>348</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>980.2199215140372</v>
+        <v>927</v>
       </c>
     </row>
     <row r="9">
@@ -1585,22 +1586,22 @@
         <v>4301</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5129.527192655975</v>
+        <v>5133.704553926043</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>3973.707610708846</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4942.837870720318</v>
+        <v>4945.549055881547</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5082.854862172061</v>
+        <v>4991</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>781.8548621720611</v>
+        <v>690</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1272.854862172061</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="10">
@@ -1616,22 +1617,22 @@
         <v>3568</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5040.006984634</v>
+        <v>5050.499628557821</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>4373.446125019273</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>4845.328238348934</v>
+        <v>4851.760564835468</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4942.667611491467</v>
+        <v>4927</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1374.667611491467</v>
+        <v>1359</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1824.667611491467</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="11">
@@ -1647,22 +1648,22 @@
         <v>2665</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4875.737788373614</v>
+        <v>4877.589375719682</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>3842.301938474977</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4407.16138324396</v>
+        <v>4407.958620029899</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4524.305484526373</v>
+        <v>4568</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1859.305484526373</v>
+        <v>1903</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2310.305484526373</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="12">
@@ -1678,22 +1679,22 @@
         <v>1712</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5296.205315245756</v>
+        <v>5211.108870911858</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2880.107471694958</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3661.11184406171</v>
+        <v>3645.90885760249</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3661.11184406171</v>
+        <v>3921</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1949.11184406171</v>
+        <v>2209</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>2355.11184406171</v>
+        <v>2615</v>
       </c>
     </row>
   </sheetData>
@@ -1808,13 +1809,13 @@
         <v>4931</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>4931</v>
+        <v>5012</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -1839,13 +1840,13 @@
         <v>4949.342562978341</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>4935.9024</v>
+        <v>5009</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>47.90239999999994</v>
+        <v>121</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>47.90239999999994</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -1870,13 +1871,13 @@
         <v>4929.764512571472</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4895.927245440001</v>
+        <v>4948</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>191.9272454400007</v>
+        <v>244</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>191.9272454400007</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6">
@@ -1892,22 +1893,22 @@
         <v>4672</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5018.22550969344</v>
+        <v>5020.6568205024</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>5102.48838127437</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>5024.039109661196</v>
+        <v>5026.339569356892</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>5018.22550969344</v>
+        <v>5050</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>346.2255096934405</v>
+        <v>378</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>346.2255096934405</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7">
@@ -1923,22 +1924,22 @@
         <v>4355</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4956.526684837317</v>
+        <v>4958.460102795075</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4796.776590799303</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4937.139329421054</v>
+        <v>4938.78271369715</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>4956.526684837317</v>
+        <v>4944</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>601.5266848373167</v>
+        <v>589</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>601.5266848373167</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -1954,22 +1955,22 @@
         <v>4018</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4966.255362243055</v>
+        <v>4968.192575116244</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>4287.219569156572</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>4836.600464340584</v>
+        <v>4837.95295893101</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>4966.255362243055</v>
+        <v>4895</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>948.2553622430551</v>
+        <v>877</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>948.2553622430551</v>
+        <v>877</v>
       </c>
     </row>
     <row r="9">
@@ -1985,22 +1986,22 @@
         <v>3810</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5337.369856403066</v>
+        <v>5340.86513299636</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>3973.707610708846</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4947.137089249114</v>
+        <v>4948.993454894378</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5239.811664614578</v>
+        <v>5096</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1429.811664614578</v>
+        <v>1286</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1429.811664614578</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="10">
@@ -2016,22 +2017,22 @@
         <v>3118</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5219.709569201153</v>
+        <v>5225.313202870895</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>4373.446125019273</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>4878.962645426544</v>
+        <v>4881.764276605292</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>5049.336107313848</v>
+        <v>5028</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1931.336107313848</v>
+        <v>1910</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1931.336107313848</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="11">
@@ -2047,22 +2048,22 @@
         <v>2214</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4795.661903931645</v>
+        <v>4803.407538798835</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>3842.301938474977</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4282.437003415775</v>
+        <v>4285.297412402457</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4410.743228544742</v>
+        <v>4470</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2196.743228544742</v>
+        <v>2256</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2196.743228544742</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="12">
@@ -2078,23 +2079,303 @@
         <v>1306</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4628.892003100621</v>
+        <v>4602.366925945735</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2880.107471694958</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3373.511205566031</v>
+        <v>3368.82792433234</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3373.511205566031</v>
+        <v>3591</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>2067.511205566031</v>
+        <v>2285</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>2067.511205566031</v>
-      </c>
+        <v>2285</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Accident Period</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Current Age</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Chain Ladder</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Initial Expected</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>BF</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Selected Ultimate</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>IBNR</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>4512</v>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>4440</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4128</v>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3732</v>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3580</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>3265</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3088</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3468</v>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>3109</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2378</v>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/demo/demo4-complete/output/selected-ultimates.xlsx
+++ b/demo/demo4-complete/output/selected-ultimates.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incurred Loss" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paid Loss" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reported Count" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closed Count" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exposure" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Incurred Loss" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Paid Loss" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Reported Count" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Closed Count" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Exposure" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,10 +141,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,30 +597,28 @@
       <c r="A3" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
+      <c r="B3" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>45008437.7</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>45571043.17125</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>63882090.39307072</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>45797105.4826305</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="7" t="n">
         <v>46543111</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>1534673.299999997</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>1534673.329999998</v>
       </c>
     </row>
@@ -622,30 +626,28 @@
       <c r="A4" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>59922623.84</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>61897224.1020876</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>63453604.66974273</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>61946874.62392249</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>61987456</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>2064832.159999996</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>2719757.659999996</v>
       </c>
     </row>
@@ -653,30 +655,28 @@
       <c r="A5" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>35372411.74</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>37751083.43963938</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>59549252.9255448</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>39124572.20170287</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>39184364</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>3811952.259999998</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>4276621.780000001</v>
       </c>
     </row>
@@ -684,30 +684,28 @@
       <c r="A6" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B6" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>55323529.15</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>61547303.11634473</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>54342744.02862492</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>60818765.14605574</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>61004941</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>5681411.850000001</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>8582581.460000001</v>
       </c>
     </row>
@@ -715,30 +713,28 @@
       <c r="A7" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>40379699.29</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>47559266.15350163</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>52619444.17055962</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>48323152.7596875</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>48041441</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>7661741.710000001</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>10116793.48</v>
       </c>
     </row>
@@ -746,30 +742,28 @@
       <c r="A8" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>34927144.1</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>44152598.66635146</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>48440622.50779771</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>45048558.82098766</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>44635788</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>9708643.899999999</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>13875288.34</v>
       </c>
     </row>
@@ -777,30 +771,28 @@
       <c r="A9" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
+      <c r="B9" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>55221806.45</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>77682093.32922915</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>46245248.98674966</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>68592732.93419862</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>72020039</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>16798232.55</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>25833024.46</v>
       </c>
     </row>
@@ -808,30 +800,28 @@
       <c r="A10" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="B10" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>27042042.17</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>45637564.02906246</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>52424249.22500541</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>48402872.73027548</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>47221287</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>20179244.83</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>24118330.15</v>
       </c>
     </row>
@@ -839,30 +829,28 @@
       <c r="A11" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
+      <c r="B11" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>21336027.8</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>48099213.74700803</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>47439177.78386472</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>47731958.98674875</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>47756784</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>26420756.2</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>29837190.28</v>
       </c>
     </row>
@@ -870,30 +858,28 @@
       <c r="A12" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
+      <c r="B12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="n">
         <v>15929923.89</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>64878397.67714732</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>36626176.32642927</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>43563088.33341151</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>47479305</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>31549381.11</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>34217948.73</v>
       </c>
     </row>
@@ -991,30 +977,28 @@
       <c r="A3" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
+      <c r="B3" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>45008437.67</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>45863597.98573</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>63882090.39307072</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>46199565.95014557</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="7" t="n">
         <v>46848515</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>1840077.329999998</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>1840077.329999998</v>
       </c>
     </row>
@@ -1022,30 +1006,28 @@
       <c r="A4" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>59267698.34</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>63014874.86046717</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>63453604.66974273</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>63040963.9075975</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>63169814</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>3902115.659999996</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>3902115.659999996</v>
       </c>
     </row>
@@ -1053,30 +1035,28 @@
       <c r="A5" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>34907742.22</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>39271138.41079672</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>59549252.9255448</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>41524229.38831383</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>40848317</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>5940574.780000001</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>5940574.780000001</v>
       </c>
     </row>
@@ -1084,30 +1064,28 @@
       <c r="A6" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B6" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>52422359.54</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>62525344.80593821</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>54342744.02862492</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>61203181.84391326</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>61785674</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>9363314.460000001</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>9363314.460000001</v>
       </c>
     </row>
@@ -1115,30 +1093,28 @@
       <c r="A7" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>37924647.52</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>49114635.01634339</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>52619444.17055962</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>49913149.97221549</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>49529430</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>11604782.48</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>11604782.48</v>
       </c>
     </row>
@@ -1146,30 +1122,28 @@
       <c r="A8" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>30760499.66</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>44166888.1278176</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>48440622.50779771</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>45464134.6791361</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>44769749</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>14009249.34</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>14009249.34</v>
       </c>
     </row>
@@ -1177,30 +1151,28 @@
       <c r="A9" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
+      <c r="B9" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>46187014.54</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>76052061.5130576</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>46245248.98674966</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>64347160.44259194</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>69294515</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>23107500.46</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>23107500.46</v>
       </c>
     </row>
@@ -1208,30 +1180,28 @@
       <c r="A10" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="B10" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>23102956.85</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>46079778.62356748</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>52424249.22500541</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>49243330.50274949</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>47820600</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>24717643.15</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>24717643.15</v>
       </c>
     </row>
@@ -1239,30 +1209,28 @@
       <c r="A11" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
+      <c r="B11" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>17919593.72</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>48751204.04683225</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>47439177.78386472</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>47921442.33593122</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>48229234</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>30309640.28</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>30309640.28</v>
       </c>
     </row>
@@ -1270,30 +1238,28 @@
       <c r="A12" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
+      <c r="B12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="n">
         <v>13261356.27</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>65485581.26640987</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>36626176.32642927</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>42470437.66225389</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>46781253</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>33519896.73</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>33519896.73</v>
       </c>
     </row>
@@ -1391,30 +1357,28 @@
       <c r="A3" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
+      <c r="B3" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>4930</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>4930</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>6554.374516225983</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>4930</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="7" t="n">
         <v>5011</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1422,30 +1386,28 @@
       <c r="A4" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>4943</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>4943</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>6320.787764849844</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>4943</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>5012</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>124</v>
       </c>
     </row>
@@ -1453,30 +1415,28 @@
       <c r="A5" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>4864</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>4911.6672</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>5759.091814286972</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>4919.891364408806</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>4956</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>252</v>
       </c>
     </row>
@@ -1484,30 +1444,28 @@
       <c r="A6" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B6" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>4886</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>4985.688569399999</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>5102.48838127437</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>4988.02397523008</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>4992</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>106</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>320</v>
       </c>
     </row>
@@ -1515,30 +1473,28 @@
       <c r="A7" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>4767</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>4971.2743580346</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>4796.776590799303</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>4964.10407999053</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>4960</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>193</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>605</v>
       </c>
     </row>
@@ -1546,30 +1502,28 @@
       <c r="A8" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>4597</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>4997.734114411615</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>4287.219569156572</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>4940.762812907539</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>4945</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>348</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>927</v>
       </c>
     </row>
@@ -1577,30 +1531,28 @@
       <c r="A9" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
+      <c r="B9" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>4301</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>5133.704553926043</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>3973.707610708846</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>4945.549055881547</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>4991</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>690</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>1181</v>
       </c>
     </row>
@@ -1608,30 +1560,28 @@
       <c r="A10" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="B10" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>3568</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>5050.499628557821</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>4373.446125019273</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>4851.760564835468</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>4927</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>1359</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>1809</v>
       </c>
     </row>
@@ -1639,30 +1589,28 @@
       <c r="A11" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
+      <c r="B11" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>2665</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>4877.589375719682</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>3842.301938474977</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>4407.958620029899</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>4568</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>1903</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>2354</v>
       </c>
     </row>
@@ -1670,30 +1618,28 @@
       <c r="A12" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
+      <c r="B12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="n">
         <v>1712</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>5211.108870911858</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>2880.107471694958</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>3645.90885760249</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>3921</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>2209</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>2615</v>
       </c>
     </row>
@@ -1791,30 +1737,28 @@
       <c r="A3" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
+      <c r="B3" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>4931</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>4931</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>6554.374516225983</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>4931</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="7" t="n">
         <v>5012</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>81</v>
       </c>
     </row>
@@ -1822,30 +1766,28 @@
       <c r="A4" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>4888</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>4935.9024</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>6320.787764849844</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>4949.342562978341</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>5009</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>121</v>
       </c>
     </row>
@@ -1853,30 +1795,28 @@
       <c r="A5" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>4704</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>4895.927245440001</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>5759.091814286972</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>4929.764512571472</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>4948</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>244</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>244</v>
       </c>
     </row>
@@ -1884,30 +1824,28 @@
       <c r="A6" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B6" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>4672</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>5020.6568205024</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>5102.48838127437</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>5026.339569356892</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>5050</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>378</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>378</v>
       </c>
     </row>
@@ -1915,30 +1853,28 @@
       <c r="A7" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>4355</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>4958.460102795075</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>4796.776590799303</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>4938.78271369715</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>4944</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>589</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>589</v>
       </c>
     </row>
@@ -1946,30 +1882,28 @@
       <c r="A8" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>4018</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>4968.192575116244</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>4287.219569156572</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>4837.95295893101</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>4895</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>877</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>877</v>
       </c>
     </row>
@@ -1977,30 +1911,28 @@
       <c r="A9" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
+      <c r="B9" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>3810</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>5340.86513299636</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>3973.707610708846</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>4948.993454894378</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>5096</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>1286</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>1286</v>
       </c>
     </row>
@@ -2008,30 +1940,28 @@
       <c r="A10" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="B10" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>3118</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>5225.313202870895</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>4373.446125019273</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>4881.764276605292</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>5028</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>1910</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>1910</v>
       </c>
     </row>
@@ -2039,30 +1969,28 @@
       <c r="A11" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
+      <c r="B11" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>2214</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>4803.407538798835</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>3842.301938474977</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>4285.297412402457</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>4470</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>2256</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>2256</v>
       </c>
     </row>
@@ -2070,30 +1998,28 @@
       <c r="A12" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
+      <c r="B12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="n">
         <v>1306</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>4602.366925945735</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>2880.107471694958</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>3368.82792433234</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>3591</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>2285</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>2285</v>
       </c>
     </row>
@@ -2191,191 +2117,171 @@
       <c r="A3" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
+      <c r="B3" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>4512</v>
       </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>4440</v>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>4128</v>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B6" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>3732</v>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="7" t="n">
         <v>3580</v>
       </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
+      <c r="B8" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>3265</v>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
+      <c r="B9" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>3088</v>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="B10" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>3468</v>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
+      <c r="B11" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>3109</v>
       </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
+      <c r="B12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="n">
         <v>2378</v>
       </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
